--- a/data_extactor/batch/1_50.xlsx
+++ b/data_extactor/batch/1_50.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sarbazi\code\sarbazi\data_extactor\batch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EBA0E2A-A91B-44BC-AAD9-4311A3C763AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88D83027-AF3F-40C5-8ADA-C8703FDF186C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="544">
   <si>
     <t>job_code</t>
   </si>
@@ -1624,6 +1624,39 @@
   </si>
   <si>
     <t>Attend or make presentations at community events to promote funeral home services or build community relationships. | Complete and maintain records, such as state-required documents, tracking documents, or product inventories. | Conduct market research and analyze industry trends. | Consult with families or friends of the deceased to arrange funeral details, such as obituary notice wording, casket selection, or plans for services. | Deliver death certificates to medical facilities or offices to obtain signatures from legally authorized persons. | Direct and supervise work of embalmers, funeral attendants, death certificate clerks, cosmetologists, or other staff. | Direct or monitor administrative, support, repair, or maintenance services for funeral homes. | Evaluate the performance of vendors, contract employees, or other service providers to ensure quality and cost-efficiency. | Explain goals, policies, or procedures to staff members. | Identify skill development needs for funeral home staff. | Interview and hire new employees. | Monitor funeral service operations to ensure that they comply with applicable policies, regulations, and laws. | Negotiate contracts for prearranged funeral services. | Offer counsel and comfort to families and friends of the deceased. | Plan and implement changes to service offerings to meet community needs or increase funeral home revenues. | Plan and implement sales promotions or other marketing strategies and activities for funeral home operations. | Respond to customer complaints, legal inquiries, payment negotiations, or other post-service matters. | Review financial statements, sales or activity reports, or other performance data to identify opportunities for cost reductions or service improvements. | Schedule funerals, burials, or cremations. | Schedule work hours for funeral home or contract employees. | Sell funeral services, products, or merchandise to clients. | Set marketing, sales, or other financial goals for funeral service establishments and monitor progress toward these goals. | Set prices or credit terms for funeral products or services.</t>
+  </si>
+  <si>
+    <t>Assembly Member | City Council Member | Commissioner | Congressman | County Supervisor | Legislator | Representative | Senator | State Representative | Tribal Council Member</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Critical Thinking | Active Listening | Speaking | Writing | Monitoring | Active Learning | Learning Strategies</t>
+  </si>
+  <si>
+    <t>Law and Government | English Language | Administration and Management | Communications and Media | Economics and Accounting | Sociology and Anthropology | Public Safety and Security | Personnel and Human Resources | History and Archeology | Psychology</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Oral Expression | Written Expression | Deductive Reasoning | Inductive Reasoning | Information Ordering | Problem Sensitivity | Near Vision | Speech Clarity | Speech Recognition | Category Flexibility | Fluency of Ideas | Originality | Selective Attention | Time Sharing | Visualization | Memorization</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Spend Time Sitting | Contact With Others | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Time Pressure | Written Letters and Memos | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Deal With External Customers or the Public in General | Coordinate or Lead Others in Accomplishing Work Activities | Work Outcomes and Results of Other Workers | Public Speaking | Conflict Situations | Level of Competition</t>
+  </si>
+  <si>
+    <t>Communications and Media | English Language | Customer and Personal Service | Sales and Marketing | Administration and Management | Personnel and Human Resources | Computers and Electronics | Psychology | Education and Training | Sociology and Anthropology</t>
+  </si>
+  <si>
+    <t>Academic Administrator | Adult Education Administrator | Curriculum Administrator | Director of Education | Education Coordinator | Education Director | Educational Program Director | Special Education Director | Vocational Education Administrator | Training Center Director</t>
+  </si>
+  <si>
+    <t>Learning management system LMS | Blackboard software | Microsoft PowerPoint | Microsoft Word | Microsoft Excel | Email software | Google Docs | Web browser software | Microsoft Outlook | Database software | Graphic presentation software | Microsoft Office software | Microsoft Access | Microsoft SharePoint | Calendar management software | Spreadsheet programs | Adobe Acrobat</t>
+  </si>
+  <si>
+    <t>Education and Training | Administration and Management | Personnel and Human Resources | English Language | Customer and Personal Service | Psychology | Law and Government | Communications and Media | Computers and Electronics | Sociology and Anthropology</t>
+  </si>
+  <si>
+    <t>Education Administrators, Kindergarten through Secondary | Education Administrators, Postsecondary | Education and Childcare Administrators, Preschool and Daycare | Instructional Coordinators | Training and Development Managers | Training and Development Specialists | Social and Community Service Managers | Medical and Health Services Managers | General and Operations Managers | Administrative Services Managers | Human Resources Managers | Chief Executives | Compliance Officers | Management Analysts | Fundraising Managers | Public Relations Managers | Educational, Guidance, and Career Counselors and Advisors | Librarians and Media Collections Specialists | Postsecondary Teachers, All Other | Special Education Teachers, All Other</t>
+  </si>
+  <si>
+    <t>Plan, direct, and coordinate the academic and administrative activities of educational programs not classified separately. | Develop and implement policies, procedures, and standards governing instructional programs. | Recruit, hire, train, supervise, and evaluate instructional and support staff. | Prepare and administer program budgets, and monitor expenditures against approved allocations. | Review and approve curricula, instructional materials, and program schedules. | Evaluate program effectiveness using enrollment, completion, and learner outcome data. | Ensure compliance with accreditation standards and applicable education regulations. | Counsel students and parents regarding enrollment, academic progress, and program requirements. | Coordinate with employers, community organizations, and funding agencies to support program goals. | Prepare reports and proposals for governing boards, funding bodies, and regulatory agencies. | Resolve disputes and disciplinary matters involving students and staff. | Direct the maintenance of student records, transcripts, and program documentation. | Plan facility use, equipment purchases, and instructional technology upgrades. | Promote programs through outreach, marketing, and community engagement activities.</t>
   </si>
 </sst>
 </file>
@@ -2091,8 +2124,23 @@
       <c r="B5" t="s">
         <v>45</v>
       </c>
+      <c r="C5" t="s">
+        <v>533</v>
+      </c>
       <c r="D5" t="s">
         <v>46</v>
+      </c>
+      <c r="E5" t="s">
+        <v>534</v>
+      </c>
+      <c r="F5" t="s">
+        <v>535</v>
+      </c>
+      <c r="G5" t="s">
+        <v>536</v>
+      </c>
+      <c r="H5" t="s">
+        <v>537</v>
       </c>
       <c r="I5" t="s">
         <v>47</v>
@@ -2222,6 +2270,18 @@
       <c r="D9" t="s">
         <v>86</v>
       </c>
+      <c r="E9" t="s">
+        <v>534</v>
+      </c>
+      <c r="F9" t="s">
+        <v>538</v>
+      </c>
+      <c r="G9" t="s">
+        <v>536</v>
+      </c>
+      <c r="H9" t="s">
+        <v>537</v>
+      </c>
       <c r="I9" t="s">
         <v>87</v>
       </c>
@@ -3114,8 +3174,32 @@
       <c r="B35" t="s">
         <v>366</v>
       </c>
+      <c r="C35" t="s">
+        <v>539</v>
+      </c>
+      <c r="D35" t="s">
+        <v>540</v>
+      </c>
+      <c r="E35" t="s">
+        <v>534</v>
+      </c>
+      <c r="F35" t="s">
+        <v>541</v>
+      </c>
+      <c r="G35" t="s">
+        <v>536</v>
+      </c>
+      <c r="H35" t="s">
+        <v>537</v>
+      </c>
+      <c r="I35" t="s">
+        <v>542</v>
+      </c>
       <c r="J35" t="s">
         <v>367</v>
+      </c>
+      <c r="K35" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
